--- a/CG_2569_บันทึกผลจริง_template.xlsx
+++ b/CG_2569_บันทึกผลจริง_template.xlsx
@@ -4176,8 +4176,12 @@
       <c r="K5" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="L5" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
@@ -4244,8 +4248,12 @@
       <c r="K6" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="L6" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
@@ -4325,8 +4333,12 @@
       <c r="K7" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="L7" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
@@ -4404,8 +4416,12 @@
       <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
@@ -4483,7 +4499,7 @@
     <col width="6.5" customWidth="1" style="19" min="5" max="16"/>
     <col width="30" customWidth="1" style="19" min="17" max="17"/>
     <col width="22" customWidth="1" style="19" min="18" max="29"/>
-    <col hidden="1" style="19" min="30" max="42"/>
+    <col hidden="1" width="13" customWidth="1" style="19" min="30" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="19">
@@ -4753,8 +4769,12 @@
       <c r="K5" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="L5" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
@@ -4836,8 +4856,12 @@
       <c r="K6" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="L6" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
@@ -4919,8 +4943,12 @@
       <c r="K7" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="L7" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
@@ -5002,8 +5030,12 @@
       <c r="K8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
@@ -5085,8 +5117,12 @@
       <c r="K9" s="11" t="n">
         <v>90</v>
       </c>
-      <c r="L9" s="11" t="n"/>
-      <c r="M9" s="11" t="n"/>
+      <c r="L9" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N9" s="11" t="n"/>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="11" t="n"/>
@@ -5168,8 +5204,12 @@
       <c r="K10" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="L10" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N10" s="11" t="n"/>
       <c r="O10" s="11" t="n"/>
       <c r="P10" s="11" t="n"/>
@@ -5247,7 +5287,7 @@
     <col width="6.5" customWidth="1" style="19" min="5" max="16"/>
     <col width="30" customWidth="1" style="19" min="17" max="17"/>
     <col width="22" customWidth="1" style="19" min="18" max="29"/>
-    <col hidden="1" style="19" min="30" max="42"/>
+    <col hidden="1" width="13" customWidth="1" style="19" min="30" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="19">
@@ -5517,8 +5557,12 @@
       <c r="K5" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="11" t="n"/>
+      <c r="L5" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N5" s="11" t="n"/>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
@@ -5600,8 +5644,12 @@
       <c r="K6" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="L6" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>70</v>
+      </c>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
@@ -5683,8 +5731,12 @@
       <c r="K7" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="L7" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>70</v>
+      </c>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
@@ -5766,8 +5818,12 @@
       <c r="K8" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
@@ -5845,7 +5901,7 @@
     <col width="6.5" customWidth="1" style="19" min="5" max="16"/>
     <col width="12" customWidth="1" style="19" min="17" max="17"/>
     <col width="22" customWidth="1" style="19" min="18" max="29"/>
-    <col hidden="1" style="19" min="30" max="42"/>
+    <col hidden="1" width="13" customWidth="1" style="19" min="30" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="19">
@@ -6132,8 +6188,12 @@
       <c r="K6" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="11" t="n"/>
+      <c r="L6" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N6" s="11" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
@@ -6194,8 +6254,12 @@
       <c r="K7" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L7" s="11" t="n"/>
-      <c r="M7" s="11" t="n"/>
+      <c r="L7" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M7" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
@@ -6271,8 +6335,12 @@
       <c r="K8" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="11" t="n"/>
+      <c r="L8" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
@@ -6371,8 +6439,12 @@
       <c r="K10" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="11" t="n"/>
-      <c r="M10" s="11" t="n"/>
+      <c r="L10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N10" s="11" t="n"/>
       <c r="O10" s="11" t="n"/>
       <c r="P10" s="11" t="n"/>
@@ -6433,8 +6505,12 @@
       <c r="K11" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
+      <c r="L11" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N11" s="11" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
@@ -6510,8 +6586,12 @@
       <c r="K12" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
+      <c r="L12" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N12" s="11" t="n"/>
       <c r="O12" s="11" t="n"/>
       <c r="P12" s="11" t="n"/>
@@ -6616,8 +6696,12 @@
       <c r="K14" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
+      <c r="L14" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N14" s="11" t="n"/>
       <c r="O14" s="11" t="n"/>
       <c r="P14" s="11" t="n"/>
@@ -6693,8 +6777,12 @@
       <c r="K15" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
+      <c r="L15" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N15" s="11" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="11" t="n"/>
@@ -6770,8 +6858,12 @@
       <c r="K16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
+      <c r="L16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" s="11" t="n"/>
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="11" t="n"/>
@@ -6847,8 +6939,12 @@
       <c r="K17" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
+      <c r="L17" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N17" s="11" t="n"/>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="n"/>
@@ -6924,8 +7020,12 @@
       <c r="K18" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
+      <c r="L18" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N18" s="11" t="n"/>
       <c r="O18" s="11" t="n"/>
       <c r="P18" s="11" t="n"/>
@@ -6994,8 +7094,12 @@
       <c r="K20" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L20" s="11" t="n"/>
-      <c r="M20" s="11" t="n"/>
+      <c r="L20" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N20" s="11" t="n"/>
       <c r="O20" s="11" t="n"/>
       <c r="P20" s="11" t="n"/>
@@ -7056,8 +7160,12 @@
       <c r="K21" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="11" t="n"/>
+      <c r="L21" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N21" s="11" t="n"/>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="11" t="n"/>
@@ -7127,8 +7235,12 @@
       <c r="K22" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L22" s="11" t="n"/>
-      <c r="M22" s="11" t="n"/>
+      <c r="L22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N22" s="11" t="n"/>
       <c r="O22" s="11" t="n"/>
       <c r="P22" s="11" t="n"/>
@@ -7189,8 +7301,12 @@
       <c r="K23" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
+      <c r="L23" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <v>50</v>
+      </c>
       <c r="N23" s="11" t="n"/>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="11" t="n"/>
@@ -7266,8 +7382,12 @@
       <c r="K24" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="11" t="n"/>
+      <c r="L24" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>50</v>
+      </c>
       <c r="N24" s="11" t="n"/>
       <c r="O24" s="11" t="n"/>
       <c r="P24" s="11" t="n"/>
@@ -7343,8 +7463,12 @@
       <c r="K25" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="11" t="n"/>
+      <c r="L25" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N25" s="11" t="n"/>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
@@ -7420,8 +7544,12 @@
       <c r="K26" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
+      <c r="L26" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M26" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N26" s="11" t="n"/>
       <c r="O26" s="11" t="n"/>
       <c r="P26" s="11" t="n"/>
@@ -7520,8 +7648,12 @@
       <c r="K28" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="11" t="n"/>
+      <c r="L28" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N28" s="11" t="n"/>
       <c r="O28" s="11" t="n"/>
       <c r="P28" s="11" t="n"/>
@@ -7578,8 +7710,12 @@
       <c r="K29" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
+      <c r="L29" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M29" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N29" s="11" t="n"/>
       <c r="O29" s="11" t="n"/>
       <c r="P29" s="11" t="n"/>
@@ -7645,8 +7781,12 @@
       <c r="K30" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="n"/>
+      <c r="L30" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M30" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N30" s="11" t="n"/>
       <c r="O30" s="11" t="n"/>
       <c r="P30" s="11" t="n"/>
@@ -7716,8 +7856,12 @@
       <c r="K31" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
+      <c r="L31" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M31" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N31" s="11" t="n"/>
       <c r="O31" s="11" t="n"/>
       <c r="P31" s="11" t="n"/>
@@ -7778,8 +7922,12 @@
       <c r="K32" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
+      <c r="L32" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N32" s="11" t="n"/>
       <c r="O32" s="11" t="n"/>
       <c r="P32" s="11" t="n"/>
@@ -7855,8 +8003,12 @@
       <c r="K33" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
+      <c r="L33" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N33" s="11" t="n"/>
       <c r="O33" s="11" t="n"/>
       <c r="P33" s="11" t="n"/>
@@ -7932,8 +8084,12 @@
       <c r="K34" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="11" t="n"/>
+      <c r="L34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N34" s="11" t="n"/>
       <c r="O34" s="11" t="n"/>
       <c r="P34" s="11" t="n"/>
@@ -8038,8 +8194,12 @@
       <c r="K36" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="11" t="n"/>
+      <c r="L36" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="N36" s="11" t="n"/>
       <c r="O36" s="11" t="n"/>
       <c r="P36" s="11" t="n"/>
@@ -8115,8 +8275,12 @@
       <c r="K37" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
+      <c r="L37" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N37" s="11" t="n"/>
       <c r="O37" s="11" t="n"/>
       <c r="P37" s="11" t="n"/>
@@ -8192,8 +8356,12 @@
       <c r="K38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L38" s="11" t="n"/>
-      <c r="M38" s="11" t="n"/>
+      <c r="L38" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N38" s="11" t="n"/>
       <c r="O38" s="11" t="n"/>
       <c r="P38" s="11" t="n"/>
@@ -8298,8 +8466,12 @@
       <c r="K40" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="11" t="n"/>
+      <c r="L40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="11" t="n"/>
       <c r="O40" s="11" t="n"/>
       <c r="P40" s="11" t="n"/>
@@ -8375,8 +8547,12 @@
       <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
+      <c r="L41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="N41" s="11" t="n"/>
       <c r="O41" s="11" t="n"/>
       <c r="P41" s="11" t="n"/>
@@ -8452,8 +8628,12 @@
       <c r="K42" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L42" s="11" t="n"/>
-      <c r="M42" s="11" t="n"/>
+      <c r="L42" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N42" s="11" t="n"/>
       <c r="O42" s="11" t="n"/>
       <c r="P42" s="11" t="n"/>
@@ -8529,8 +8709,12 @@
       <c r="K43" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
+      <c r="L43" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N43" s="11" t="n"/>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="11" t="n"/>
@@ -8606,8 +8790,12 @@
       <c r="K44" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
+      <c r="L44" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M44" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N44" s="11" t="n"/>
       <c r="O44" s="11" t="n"/>
       <c r="P44" s="11" t="n"/>
@@ -8712,8 +8900,12 @@
       <c r="K46" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L46" s="11" t="n"/>
-      <c r="M46" s="11" t="n"/>
+      <c r="L46" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N46" s="11" t="n"/>
       <c r="O46" s="11" t="n"/>
       <c r="P46" s="11" t="n"/>
@@ -8789,8 +8981,12 @@
       <c r="K47" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
+      <c r="L47" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N47" s="11" t="n"/>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="11" t="n"/>
@@ -8866,8 +9062,12 @@
       <c r="K48" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L48" s="11" t="n"/>
-      <c r="M48" s="11" t="n"/>
+      <c r="L48" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M48" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N48" s="11" t="n"/>
       <c r="O48" s="11" t="n"/>
       <c r="P48" s="11" t="n"/>
@@ -8972,8 +9172,12 @@
       <c r="K50" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="L50" s="11" t="n"/>
-      <c r="M50" s="11" t="n"/>
+      <c r="L50" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="M50" s="11" t="n">
+        <v>85</v>
+      </c>
       <c r="N50" s="11" t="n"/>
       <c r="O50" s="11" t="n"/>
       <c r="P50" s="11" t="n"/>
@@ -9049,8 +9253,12 @@
       <c r="K51" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
+      <c r="L51" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M51" s="11" t="n">
+        <v>40</v>
+      </c>
       <c r="N51" s="11" t="n"/>
       <c r="O51" s="11" t="n"/>
       <c r="P51" s="11" t="n"/>
@@ -9090,15 +9298,15 @@
   <mergeCells count="11">
     <mergeCell ref="A9:Q9"/>
     <mergeCell ref="A27:Q27"/>
-    <mergeCell ref="A5:Q5"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A39:Q39"/>
     <mergeCell ref="A35:Q35"/>
+    <mergeCell ref="A13:Q13"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A19:Q19"/>
     <mergeCell ref="A49:Q49"/>
     <mergeCell ref="A45:Q45"/>
-    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="A5:Q5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E5:P51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" type="whole">

--- a/CG_2569_บันทึกผลจริง_template.xlsx
+++ b/CG_2569_บันทึกผลจริง_template.xlsx
@@ -4182,7 +4182,9 @@
       <c r="M5" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="8" t="n"/>
@@ -4254,7 +4256,9 @@
       <c r="M6" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
       <c r="Q6" s="8" t="n"/>
@@ -4339,7 +4343,9 @@
       <c r="M7" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="8" t="n"/>
@@ -4422,7 +4428,9 @@
       <c r="M8" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N8" s="11" t="n"/>
+      <c r="N8" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="8" t="n"/>
@@ -4775,7 +4783,9 @@
       <c r="M5" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="8" t="n"/>
@@ -4862,7 +4872,9 @@
       <c r="M6" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
       <c r="Q6" s="8" t="n"/>
@@ -4949,7 +4961,9 @@
       <c r="M7" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>80</v>
+      </c>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="8" t="n"/>
@@ -5036,7 +5050,9 @@
       <c r="M8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="11" t="n"/>
+      <c r="N8" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="8" t="n"/>
@@ -5123,7 +5139,9 @@
       <c r="M9" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N9" s="11" t="n"/>
+      <c r="N9" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O9" s="11" t="n"/>
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="8" t="n"/>
@@ -5210,7 +5228,9 @@
       <c r="M10" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N10" s="11" t="n"/>
+      <c r="N10" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O10" s="11" t="n"/>
       <c r="P10" s="11" t="n"/>
       <c r="Q10" s="8" t="n"/>
@@ -5563,7 +5583,9 @@
       <c r="M5" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N5" s="11" t="n"/>
+      <c r="N5" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O5" s="11" t="n"/>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="8" t="n"/>
@@ -5650,7 +5672,9 @@
       <c r="M6" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="11" t="n">
+        <v>80</v>
+      </c>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
       <c r="Q6" s="8" t="n"/>
@@ -5737,7 +5761,9 @@
       <c r="M7" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>80</v>
+      </c>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="8" t="n"/>
@@ -5824,7 +5850,9 @@
       <c r="M8" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N8" s="11" t="n"/>
+      <c r="N8" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="8" t="n"/>
@@ -6194,7 +6222,9 @@
       <c r="M6" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N6" s="11" t="n"/>
+      <c r="N6" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="11" t="n"/>
       <c r="Q6" s="8" t="n"/>
@@ -6260,7 +6290,9 @@
       <c r="M7" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N7" s="11" t="n"/>
+      <c r="N7" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="8" t="n"/>
@@ -6341,7 +6373,9 @@
       <c r="M8" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N8" s="11" t="n"/>
+      <c r="N8" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="11" t="n"/>
       <c r="Q8" s="8" t="n"/>
@@ -6445,7 +6479,9 @@
       <c r="M10" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N10" s="11" t="n"/>
+      <c r="N10" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O10" s="11" t="n"/>
       <c r="P10" s="11" t="n"/>
       <c r="Q10" s="8" t="n"/>
@@ -6511,7 +6547,9 @@
       <c r="M11" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N11" s="11" t="n"/>
+      <c r="N11" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="11" t="n"/>
       <c r="Q11" s="8" t="n"/>
@@ -6592,7 +6630,9 @@
       <c r="M12" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N12" s="11" t="n"/>
+      <c r="N12" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O12" s="11" t="n"/>
       <c r="P12" s="11" t="n"/>
       <c r="Q12" s="8" t="n"/>
@@ -6702,7 +6742,9 @@
       <c r="M14" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N14" s="11" t="n"/>
+      <c r="N14" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O14" s="11" t="n"/>
       <c r="P14" s="11" t="n"/>
       <c r="Q14" s="8" t="n"/>
@@ -6783,7 +6825,9 @@
       <c r="M15" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N15" s="11" t="n"/>
+      <c r="N15" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="11" t="n"/>
       <c r="Q15" s="8" t="n"/>
@@ -6864,7 +6908,9 @@
       <c r="M16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="11" t="n"/>
+      <c r="N16" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="O16" s="11" t="n"/>
       <c r="P16" s="11" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -6945,7 +6991,9 @@
       <c r="M17" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N17" s="11" t="n"/>
+      <c r="N17" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O17" s="11" t="n"/>
       <c r="P17" s="11" t="n"/>
       <c r="Q17" s="8" t="n"/>
@@ -7026,7 +7074,9 @@
       <c r="M18" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N18" s="11" t="n"/>
+      <c r="N18" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O18" s="11" t="n"/>
       <c r="P18" s="11" t="n"/>
       <c r="Q18" s="8" t="n"/>
@@ -7100,7 +7150,9 @@
       <c r="M20" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N20" s="11" t="n"/>
+      <c r="N20" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O20" s="11" t="n"/>
       <c r="P20" s="11" t="n"/>
       <c r="Q20" s="8" t="n"/>
@@ -7166,7 +7218,9 @@
       <c r="M21" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N21" s="11" t="n"/>
+      <c r="N21" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="11" t="n"/>
       <c r="Q21" s="8" t="n"/>
@@ -7241,7 +7295,9 @@
       <c r="M22" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N22" s="11" t="n"/>
+      <c r="N22" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O22" s="11" t="n"/>
       <c r="P22" s="11" t="n"/>
       <c r="Q22" s="8" t="n"/>
@@ -7307,7 +7363,9 @@
       <c r="M23" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N23" s="11" t="n"/>
+      <c r="N23" s="11" t="n">
+        <v>70</v>
+      </c>
       <c r="O23" s="11" t="n"/>
       <c r="P23" s="11" t="n"/>
       <c r="Q23" s="8" t="n"/>
@@ -7388,7 +7446,9 @@
       <c r="M24" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="N24" s="11" t="n"/>
+      <c r="N24" s="11" t="n">
+        <v>70</v>
+      </c>
       <c r="O24" s="11" t="n"/>
       <c r="P24" s="11" t="n"/>
       <c r="Q24" s="8" t="n"/>
@@ -7469,7 +7529,9 @@
       <c r="M25" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N25" s="11" t="n"/>
+      <c r="N25" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O25" s="11" t="n"/>
       <c r="P25" s="11" t="n"/>
       <c r="Q25" s="8" t="n"/>
@@ -7550,7 +7612,9 @@
       <c r="M26" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N26" s="11" t="n"/>
+      <c r="N26" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O26" s="11" t="n"/>
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="8" t="n"/>
@@ -7654,7 +7718,9 @@
       <c r="M28" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N28" s="11" t="n"/>
+      <c r="N28" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O28" s="11" t="n"/>
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="8" t="n"/>
@@ -7716,7 +7782,9 @@
       <c r="M29" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N29" s="11" t="n"/>
+      <c r="N29" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O29" s="11" t="n"/>
       <c r="P29" s="11" t="n"/>
       <c r="Q29" s="8" t="n"/>
@@ -7787,7 +7855,9 @@
       <c r="M30" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N30" s="11" t="n"/>
+      <c r="N30" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O30" s="11" t="n"/>
       <c r="P30" s="11" t="n"/>
       <c r="Q30" s="8" t="n"/>
@@ -7862,7 +7932,9 @@
       <c r="M31" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N31" s="11" t="n"/>
+      <c r="N31" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O31" s="11" t="n"/>
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="8" t="n"/>
@@ -7928,7 +8000,9 @@
       <c r="M32" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N32" s="11" t="n"/>
+      <c r="N32" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O32" s="11" t="n"/>
       <c r="P32" s="11" t="n"/>
       <c r="Q32" s="8" t="n"/>
@@ -8009,7 +8083,9 @@
       <c r="M33" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N33" s="11" t="n"/>
+      <c r="N33" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O33" s="11" t="n"/>
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="8" t="n"/>
@@ -8090,7 +8166,9 @@
       <c r="M34" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N34" s="11" t="n"/>
+      <c r="N34" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O34" s="11" t="n"/>
       <c r="P34" s="11" t="n"/>
       <c r="Q34" s="8" t="n"/>
@@ -8200,7 +8278,9 @@
       <c r="M36" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="N36" s="11" t="n"/>
+      <c r="N36" s="11" t="n">
+        <v>100</v>
+      </c>
       <c r="O36" s="11" t="n"/>
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="8" t="n"/>
@@ -8281,7 +8361,9 @@
       <c r="M37" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N37" s="11" t="n"/>
+      <c r="N37" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O37" s="11" t="n"/>
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="8" t="n"/>
@@ -8362,7 +8444,9 @@
       <c r="M38" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N38" s="11" t="n"/>
+      <c r="N38" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O38" s="11" t="n"/>
       <c r="P38" s="11" t="n"/>
       <c r="Q38" s="8" t="n"/>
@@ -8472,7 +8556,9 @@
       <c r="M40" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="11" t="n"/>
+      <c r="N40" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="O40" s="11" t="n"/>
       <c r="P40" s="11" t="n"/>
       <c r="Q40" s="8" t="n"/>
@@ -8553,7 +8639,9 @@
       <c r="M41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="11" t="n"/>
+      <c r="N41" s="11" t="n">
+        <v>30</v>
+      </c>
       <c r="O41" s="11" t="n"/>
       <c r="P41" s="11" t="n"/>
       <c r="Q41" s="8" t="n"/>
@@ -8634,7 +8722,9 @@
       <c r="M42" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N42" s="11" t="n"/>
+      <c r="N42" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O42" s="11" t="n"/>
       <c r="P42" s="11" t="n"/>
       <c r="Q42" s="8" t="n"/>
@@ -8715,7 +8805,9 @@
       <c r="M43" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N43" s="11" t="n"/>
+      <c r="N43" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O43" s="11" t="n"/>
       <c r="P43" s="11" t="n"/>
       <c r="Q43" s="8" t="n"/>
@@ -8796,7 +8888,9 @@
       <c r="M44" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N44" s="11" t="n"/>
+      <c r="N44" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O44" s="11" t="n"/>
       <c r="P44" s="11" t="n"/>
       <c r="Q44" s="8" t="n"/>
@@ -8906,7 +9000,9 @@
       <c r="M46" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N46" s="11" t="n"/>
+      <c r="N46" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O46" s="11" t="n"/>
       <c r="P46" s="11" t="n"/>
       <c r="Q46" s="8" t="n"/>
@@ -8987,7 +9083,9 @@
       <c r="M47" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N47" s="11" t="n"/>
+      <c r="N47" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="11" t="n"/>
       <c r="Q47" s="8" t="n"/>
@@ -9068,7 +9166,9 @@
       <c r="M48" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N48" s="11" t="n"/>
+      <c r="N48" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O48" s="11" t="n"/>
       <c r="P48" s="11" t="n"/>
       <c r="Q48" s="8" t="n"/>
@@ -9178,7 +9278,9 @@
       <c r="M50" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="N50" s="11" t="n"/>
+      <c r="N50" s="11" t="n">
+        <v>90</v>
+      </c>
       <c r="O50" s="11" t="n"/>
       <c r="P50" s="11" t="n"/>
       <c r="Q50" s="8" t="n"/>
@@ -9259,7 +9361,9 @@
       <c r="M51" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="N51" s="11" t="n"/>
+      <c r="N51" s="11" t="n">
+        <v>60</v>
+      </c>
       <c r="O51" s="11" t="n"/>
       <c r="P51" s="11" t="n"/>
       <c r="Q51" s="8" t="n"/>
@@ -9301,12 +9405,12 @@
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="A39:Q39"/>
     <mergeCell ref="A35:Q35"/>
-    <mergeCell ref="A13:Q13"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A19:Q19"/>
     <mergeCell ref="A49:Q49"/>
     <mergeCell ref="A45:Q45"/>
     <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A13:Q13"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E5:P51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ค่าไม่ถูกต้อง" error="กรอกค่าร้อยละ 0–100" promptTitle="บันทึกผลจริง" prompt="ผลจริงสะสม (%) 0–100" type="whole">
